--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>ObservationalStudyProtocolVersion; Study;
@@ -324,16 +324,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -370,7 +370,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -390,16 +390,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ResearchStudy.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子</t>
-  </si>
-  <si>
-    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
   </si>
   <si>
     <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
@@ -419,7 +419,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースのバージョンが最後に変更されたとき」</t>
+    <t>リソースのバージョンが最後に変更されたとき</t>
   </si>
   <si>
     <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
@@ -444,8 +444,8 @@
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
   </si>
   <si>
-    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
-この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
   </si>
   <si>
     <t>Meta.source</t>
@@ -513,7 +513,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/common-tags</t>
@@ -632,7 +632,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -660,10 +660,10 @@
 </t>
   </si>
   <si>
-    <t>研究のためのビジネス識別子 / Business Identifier for study</t>
-  </si>
-  <si>
-    <t>スポンサーまたは他のシステムによるこの調査研究に割り当てられた識別子。 / Identifiers assigned to this research study by the sponsor or other systems.</t>
+    <t>研究のためのビジネスidentifier / Business Identifier for study</t>
+  </si>
+  <si>
+    <t>スポンサーまたは他のシステムによるこの調査研究に割り当てられたidentifier。 / Identifiers assigned to this research study by the sponsor or other systems.</t>
   </si>
   <si>
     <t>さまざまな参加システムで知られており、サーバー全体で一貫性を保っている方法で、調査研究を特定できます。 / Allows identification of the research study as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -703,7 +703,7 @@
 </t>
   </si>
   <si>
-    <t>研究の実行に従った手順 / Steps followed in executing study</t>
+    <t>研究の実行に従ったプロシジャー（処置等） / Steps followed in executing study</t>
   </si>
   <si>
     <t>一連のステップは、研究の実行の一部として実行されると予想されます。 / The set of steps expected to be performed as part of the execution of the study.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -508,15 +508,6 @@
   </si>
   <si>
     <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -800,6 +791,9 @@
   </si>
   <si>
     <t>臨床試験におけるヒトでの最初の実験的使用から市場後の評価への治療の進行の段階。 / The stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>臨床試験におけるヒトの初期実験的使用から市場後の評価への治療の進行の段階のコード。 / Codes for the stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
@@ -2998,31 +2992,31 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3054,10 +3048,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3083,13 +3077,13 @@
         <v>134</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3139,7 +3133,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3171,10 +3165,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3197,16 +3191,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3232,31 +3226,31 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3288,14 +3282,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3314,16 +3308,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3373,7 +3367,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3394,7 +3388,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3405,14 +3399,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3431,16 +3425,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3490,7 +3484,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3511,7 +3505,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3522,10 +3516,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3551,13 +3545,13 @@
         <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3607,7 +3601,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3619,7 +3613,7 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
@@ -3628,7 +3622,7 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3639,10 +3633,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3668,16 +3662,16 @@
         <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -3726,7 +3720,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3738,7 +3732,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -3747,7 +3741,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3758,10 +3752,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3784,17 +3778,17 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3843,7 +3837,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3858,27 +3852,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3904,10 +3898,10 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3958,7 +3952,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3973,7 +3967,7 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -3982,7 +3976,7 @@
         <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -3990,10 +3984,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4016,13 +4010,13 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4073,7 +4067,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4088,16 +4082,16 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4105,14 +4099,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4131,17 +4125,17 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4190,7 +4184,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4205,13 +4199,13 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4222,10 +4216,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4248,13 +4242,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4281,13 +4275,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4305,7 +4299,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>91</v>
@@ -4320,27 +4314,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4363,13 +4357,13 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4399,10 +4393,10 @@
         <v>150</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4420,7 +4414,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4435,7 +4429,7 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -4452,10 +4446,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4478,13 +4472,13 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4511,13 +4505,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4535,7 +4529,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4550,7 +4544,7 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
@@ -4559,7 +4553,7 @@
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -4567,10 +4561,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4593,13 +4587,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4626,10 +4620,10 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>81</v>
@@ -4650,7 +4644,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4665,7 +4659,7 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
@@ -4674,7 +4668,7 @@
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -4682,10 +4676,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4708,13 +4702,13 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4741,10 +4735,10 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>81</v>
@@ -4765,7 +4759,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4780,27 +4774,27 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4823,13 +4817,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4856,13 +4850,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4880,7 +4874,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4895,7 +4889,7 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
@@ -4904,18 +4898,18 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4938,13 +4932,13 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4995,7 +4989,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5010,7 +5004,7 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
@@ -5019,7 +5013,7 @@
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5027,10 +5021,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5053,13 +5047,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5110,7 +5104,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5125,7 +5119,7 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
@@ -5134,7 +5128,7 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5142,10 +5136,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5168,13 +5162,13 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5201,10 +5195,10 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>81</v>
@@ -5225,7 +5219,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5240,7 +5234,7 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>81</v>
@@ -5249,7 +5243,7 @@
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5257,10 +5251,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5283,13 +5277,13 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5319,10 +5313,10 @@
         <v>150</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5340,7 +5334,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5355,7 +5349,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -5372,10 +5366,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5398,13 +5392,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5455,7 +5449,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5470,7 +5464,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -5479,7 +5473,7 @@
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -5487,14 +5481,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5513,16 +5507,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5572,7 +5566,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5587,31 +5581,31 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5630,13 +5624,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5687,7 +5681,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5702,27 +5696,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5745,13 +5739,13 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5802,7 +5796,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5817,27 +5811,27 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5860,13 +5854,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5917,7 +5911,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5932,7 +5926,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -5941,18 +5935,18 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5975,13 +5969,13 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6032,7 +6026,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6047,27 +6041,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6090,13 +6084,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6123,13 +6117,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6147,7 +6141,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6162,27 +6156,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6205,13 +6199,13 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6262,7 +6256,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6277,13 +6271,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6294,10 +6288,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6320,13 +6314,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6377,7 +6371,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6392,7 +6386,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
@@ -6401,7 +6395,7 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6409,10 +6403,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6438,10 +6432,10 @@
         <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6524,10 +6518,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6553,13 +6547,13 @@
         <v>112</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6621,7 +6615,7 @@
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -6641,14 +6635,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6670,16 +6664,16 @@
         <v>112</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6728,7 +6722,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6740,7 +6734,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -6749,7 +6743,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -6760,10 +6754,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6789,10 +6783,10 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6843,7 +6837,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>91</v>
@@ -6858,7 +6852,7 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
@@ -6867,7 +6861,7 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -6875,10 +6869,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6901,13 +6895,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6958,7 +6952,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6973,7 +6967,7 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>81</v>
@@ -6982,7 +6976,7 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -6990,10 +6984,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7019,10 +7013,10 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7073,7 +7067,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7088,7 +7082,7 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
@@ -7097,7 +7091,7 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7105,10 +7099,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7131,13 +7125,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7188,7 +7182,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7203,7 +7197,7 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
@@ -7220,10 +7214,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7249,10 +7243,10 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7335,10 +7329,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7364,13 +7358,13 @@
         <v>112</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7432,7 +7426,7 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -7452,14 +7446,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7481,16 +7475,16 @@
         <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7539,7 +7533,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7551,7 +7545,7 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -7560,7 +7554,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -7571,10 +7565,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7600,10 +7594,10 @@
         <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7654,7 +7648,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7669,7 +7663,7 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
@@ -7686,10 +7680,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7712,13 +7706,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7745,13 +7739,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -7769,7 +7763,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7784,7 +7778,7 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -438,7 +438,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースがどこから来たかを特定する」</t>
+    <t>リソースがどこから来たかを特定する</t>
   </si>
   <si>
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>ObservationalStudyProtocolVersion; Study;
@@ -390,7 +390,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ResearchStudy.meta.versionId</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -1596,17 +1596,17 @@
   <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.0234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.0234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="32.32421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1615,27 +1615,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="171.58203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.97265625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="147.1015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.12890625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="207.0625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="97.8125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="181.859375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="177.51953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="83.85546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="155.9140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -454,7 +454,7 @@
     <t>ResearchStudy.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -492,7 +492,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -550,7 +550,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -690,7 +690,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition)
+    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -778,7 +778,7 @@
     <t>研究の主な意図をコードします。 / Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.primaryPurposeTypeCode</t>
@@ -799,7 +799,7 @@
     <t>臨床試験におけるヒトの初期実験的使用から市場後の評価への治療の進行の段階のコード。 / Codes for the stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-phase</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-phase|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.phaseCode</t>
@@ -859,7 +859,7 @@
     <t>状態または診断の識別。 / Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>StudyCondition.code</t>
@@ -936,7 +936,7 @@
     <t>このアーティファクトが使用することを目的としている国と地域。 / Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.participatingLocationCode</t>
@@ -968,7 +968,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Group)
+    <t xml:space="preserve">Reference(Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1025,7 +1025,7 @@
     <t>ResearchStudy.sponsor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1069,7 +1069,7 @@
     <t>ResearchStudy.site</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1100,7 +1100,7 @@
     <t>研究が時期尚早に終了した理由をコードします。 / Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
   </si>
   <si>
     <t>StudyOverallStatus.studyStoppedReasonCode</t>
@@ -1273,7 +1273,7 @@
     <t>学習目標の種類をコードします。 / Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
   </si>
   <si>
     <t>StudyObjective.typeCode</t>
@@ -1606,7 +1606,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="32.32421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="41.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1621,7 +1621,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="147.1015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-researchstudy.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -2461,7 +2461,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -7795,12 +7795,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO53">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
